--- a/config/excel/mall.xlsx
+++ b/config/excel/mall.xlsx
@@ -1,10 +1,15 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
+<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:dbsheet="http://web.wps.cn/et/2021/dbsheet" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" mc:Ignorable="x15">
   <fileVersion appName="xl" lastEdited="3" lowestEdited="5" rupBuild="9302"/>
   <workbookPr/>
+  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
+    <mc:Choice Requires="x15">
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="F:\go\gforgame\config\excel\"/>
+    </mc:Choice>
+  </mc:AlternateContent>
   <bookViews>
-    <workbookView windowWidth="28800" windowHeight="14175"/>
+    <workbookView windowWidth="28800" windowHeight="11775"/>
   </bookViews>
   <sheets>
     <sheet name="mall" sheetId="1" r:id="rId1"/>
@@ -27,7 +32,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="36" uniqueCount="34">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="36" uniqueCount="33">
   <si>
     <t xml:space="preserve"> 字段</t>
   </si>
@@ -53,9 +58,6 @@
     <t>string</t>
   </si>
   <si>
-    <t>json</t>
-  </si>
-  <si>
     <t>HEADER</t>
   </si>
   <si>
@@ -77,46 +79,46 @@
     <t>降龙十八掌</t>
   </si>
   <si>
-    <t>[{"type":"Currency","value":"Diamond_100"}]</t>
-  </si>
-  <si>
-    <t>[{"type":"Item","value":"1001_1"}]</t>
+    <t>Currency_Diamond_103</t>
+  </si>
+  <si>
+    <t>item_1001_1</t>
   </si>
   <si>
     <t>九阴真经</t>
   </si>
   <si>
-    <t>[{"type":"Currency","value":"Diamond_101"}]</t>
-  </si>
-  <si>
-    <t>[{"type":"Item","value":"1002_1"}]</t>
+    <t>Currency_Diamond_104</t>
+  </si>
+  <si>
+    <t>item_1001_2</t>
   </si>
   <si>
     <t>九阳神功</t>
   </si>
   <si>
-    <t>[{"type":"Currency","value":"Diamond_102"}]</t>
-  </si>
-  <si>
-    <t>[{"type":"Item","value":"1003_1"}]</t>
+    <t>Currency_Diamond_105</t>
+  </si>
+  <si>
+    <t>item_1001_3</t>
   </si>
   <si>
     <t>太玄经</t>
   </si>
   <si>
-    <t>[{"type":"Currency","value":"Diamond_103"}]</t>
-  </si>
-  <si>
-    <t>[{"type":"Item","value":"1004_1"}]</t>
+    <t>Currency_Diamond_106</t>
+  </si>
+  <si>
+    <t>item_1001_4</t>
   </si>
   <si>
     <t>小无相功</t>
   </si>
   <si>
-    <t>[{"type":"Currency","value":"Diamond_104"}]</t>
-  </si>
-  <si>
-    <t>[{"type":"Item","value":"1005_1"}]</t>
+    <t>Currency_Diamond_107</t>
+  </si>
+  <si>
+    <t>item_1001_5</t>
   </si>
   <si>
     <t>END</t>
@@ -125,10 +127,10 @@
     <t>葵花宝典</t>
   </si>
   <si>
-    <t>[{"type":"Currency","value":"Diamond_105"}]</t>
-  </si>
-  <si>
-    <t>[{"type":"Item","value":"1006_1"}]</t>
+    <t>Currency_Diamond_108</t>
+  </si>
+  <si>
+    <t>item_1001_6</t>
   </si>
 </sst>
 </file>
@@ -1309,7 +1311,7 @@
         <v>5</v>
       </c>
     </row>
-    <row r="2" spans="2:6">
+    <row r="2" spans="1:6">
       <c r="B2" t="s">
         <v>6</v>
       </c>
@@ -1320,135 +1322,135 @@
         <v>6</v>
       </c>
       <c r="E2" t="s">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="F2" t="s">
-        <v>8</v>
+        <v>7</v>
       </c>
     </row>
     <row r="3" spans="1:6">
       <c r="A3" t="s">
+        <v>8</v>
+      </c>
+      <c r="B3" t="s">
         <v>9</v>
       </c>
-      <c r="B3" t="s">
+      <c r="C3" t="s">
         <v>10</v>
       </c>
-      <c r="C3" t="s">
+      <c r="D3" t="s">
         <v>11</v>
       </c>
-      <c r="D3" t="s">
+      <c r="E3" t="s">
         <v>12</v>
       </c>
-      <c r="E3" t="s">
+      <c r="F3" t="s">
         <v>13</v>
       </c>
-      <c r="F3" t="s">
-        <v>14</v>
-      </c>
     </row>
-    <row r="4" spans="2:6">
+    <row r="4" spans="1:6">
       <c r="B4">
         <v>1</v>
       </c>
       <c r="C4" t="s">
-        <v>15</v>
+        <v>14</v>
       </c>
       <c r="D4">
         <v>1</v>
       </c>
       <c r="E4" t="s">
+        <v>15</v>
+      </c>
+      <c r="F4" t="s">
         <v>16</v>
       </c>
-      <c r="F4" t="s">
-        <v>17</v>
-      </c>
     </row>
-    <row r="5" customFormat="1" spans="2:6">
+    <row r="5" customFormat="1" spans="1:6">
       <c r="B5">
         <v>2</v>
       </c>
       <c r="C5" t="s">
-        <v>18</v>
+        <v>17</v>
       </c>
       <c r="D5">
         <v>2</v>
       </c>
       <c r="E5" t="s">
+        <v>18</v>
+      </c>
+      <c r="F5" t="s">
         <v>19</v>
       </c>
-      <c r="F5" t="s">
-        <v>20</v>
-      </c>
     </row>
-    <row r="6" customFormat="1" spans="2:6">
+    <row r="6" customFormat="1" spans="1:6">
       <c r="B6">
         <v>3</v>
       </c>
       <c r="C6" t="s">
-        <v>21</v>
+        <v>20</v>
       </c>
       <c r="D6">
         <v>2</v>
       </c>
       <c r="E6" t="s">
+        <v>21</v>
+      </c>
+      <c r="F6" t="s">
         <v>22</v>
       </c>
-      <c r="F6" t="s">
-        <v>23</v>
-      </c>
     </row>
-    <row r="7" spans="2:6">
+    <row r="7" spans="1:6">
       <c r="B7">
         <v>4</v>
       </c>
       <c r="C7" t="s">
-        <v>24</v>
+        <v>23</v>
       </c>
       <c r="D7">
         <v>2</v>
       </c>
       <c r="E7" t="s">
+        <v>24</v>
+      </c>
+      <c r="F7" t="s">
         <v>25</v>
       </c>
-      <c r="F7" t="s">
-        <v>26</v>
-      </c>
     </row>
-    <row r="8" spans="2:6">
+    <row r="8" spans="1:6">
       <c r="B8">
         <v>5</v>
       </c>
       <c r="C8" t="s">
-        <v>27</v>
+        <v>26</v>
       </c>
       <c r="D8">
         <v>2</v>
       </c>
       <c r="E8" t="s">
+        <v>27</v>
+      </c>
+      <c r="F8" t="s">
         <v>28</v>
-      </c>
-      <c r="F8" t="s">
-        <v>29</v>
       </c>
     </row>
     <row r="9" spans="1:6">
       <c r="A9" t="s">
-        <v>30</v>
+        <v>29</v>
       </c>
       <c r="B9">
         <v>6</v>
       </c>
       <c r="C9" t="s">
-        <v>31</v>
+        <v>30</v>
       </c>
       <c r="D9">
         <v>2</v>
       </c>
       <c r="E9" t="s">
+        <v>31</v>
+      </c>
+      <c r="F9" t="s">
         <v>32</v>
-      </c>
-      <c r="F9" t="s">
-        <v>33</v>
       </c>
     </row>
   </sheetData>
